--- a/elite-data/manifest-templates/EL_template_AssayMetagenomicsTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_AssayMetagenomicsTemplate.xlsx
@@ -348,10 +348,10 @@
     <t>MULTIseq</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>Not specified</t>
@@ -384,7 +384,7 @@
     <t>totalRNA</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
 </sst>
 </file>
